--- a/src_files/data_files/unittypedata_nuclear-lwr-smr.xlsx
+++ b/src_files/data_files/unittypedata_nuclear-lwr-smr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\backbone\north_european_model\src_files\data_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83695669-5E11-4839-B2EE-472B1B0A3B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CE0EA1-44D0-49F3-A24A-0981BC4F6859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="5" r:id="rId1"/>
@@ -138,9 +138,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="246">
   <si>
-    <t>Generator_ID</t>
-  </si>
-  <si>
     <t>vomCosts</t>
   </si>
   <si>
@@ -874,6 +871,9 @@
   </si>
   <si>
     <t>In principle, startup and shutdown numbers for NPPs over the lifetime are also limited to minimize thermal/corrosive stress on the reactor core (~20 hot starts per year, ~1-2 cold starts per year), but how these apply to SMRs is unknown.</t>
+  </si>
+  <si>
+    <t>## Description</t>
   </si>
 </sst>
 </file>
@@ -1476,398 +1476,398 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>48</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C13" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C14" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C15" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C16" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C19" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C20" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C21" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>199</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="19" t="s">
         <v>53</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B39" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C41" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C42" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C43" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C44" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B45" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B46" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B47" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C51" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D52" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D53" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D54" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C55" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D56" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D57" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C65" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D66" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D67" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D68" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D69" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C70" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D71" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D72" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="73" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D73" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="74" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D74" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D75" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C76" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D77" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D78" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D79" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D80" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="81" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D81" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1885,239 +1885,239 @@
   <sheetData>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B58" s="20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B59" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B62" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B64" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B66" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B67" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B68" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B69" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B71" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B73" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B74" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B75" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B76" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B77" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B78" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B79" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B80" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B82" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B83" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B84" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B85" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B86" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B87" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B88" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B89" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B90" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B91" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B92" s="20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B93" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B94" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B95" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B96" s="20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.25">
@@ -2127,146 +2127,146 @@
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B101" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B102" s="20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B103" s="20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B104" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B105" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" s="20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B107" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B108" s="20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B109" s="20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B110" s="20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B111" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B112" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B113" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B114" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B116" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B117" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B118" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B119" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B120" s="20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B121" s="20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B122" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B123" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B124" s="20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B125" s="20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -2276,65 +2276,65 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B127" s="20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B128" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B129" s="20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B130" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B131" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B132" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B133" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B134" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B135" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B136" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B137" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B138" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -2344,25 +2344,25 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B140" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B141" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B142" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B143" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2405,162 +2405,162 @@
   <sheetData>
     <row r="1" spans="1:46" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="L1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="U1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="R1" s="11" t="s">
+      <c r="V1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="AK1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="U1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="V1" s="10" t="s">
+      <c r="AM1" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN1" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO1" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP1" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="AQ1" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="AR1" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="AS1" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="AT1" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE1" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF1" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AG1" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH1" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="AI1" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ1" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK1" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="AL1" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM1" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN1" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="AO1" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="AP1" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="AQ1" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="AR1" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="AS1" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="AT1" s="11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O2" s="21">
         <v>0.31</v>
@@ -2648,22 +2648,22 @@
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O3" s="21">
         <v>0.32</v>
@@ -2751,22 +2751,22 @@
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O4" s="21">
         <v>0.33</v>
@@ -2852,27 +2852,27 @@
         <v>0.9</v>
       </c>
       <c r="AT4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" t="s">
         <v>78</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D5" t="s">
-        <v>79</v>
-      </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O5" s="21">
         <v>0.34</v>
@@ -2960,22 +2960,22 @@
     </row>
     <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O6" s="21">
         <v>0.36</v>
@@ -3063,25 +3063,25 @@
     </row>
     <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" s="22">
         <v>0.61</v>
@@ -3178,25 +3178,25 @@
     </row>
     <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O8" s="21">
         <v>0.81</v>
@@ -3293,25 +3293,25 @@
     </row>
     <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O9" s="21">
         <v>0.875</v>
@@ -3406,30 +3406,30 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AT9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O10" s="21">
         <v>0.9</v>
@@ -3526,25 +3526,25 @@
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O11" s="21">
         <v>0.94</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O12" s="21">
         <v>0.23</v>
@@ -3744,22 +3744,22 @@
     </row>
     <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O13" s="21">
         <v>0.31</v>
@@ -3847,22 +3847,22 @@
     </row>
     <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O14" s="21">
         <v>0.33</v>
@@ -3948,27 +3948,27 @@
         <v>0.9</v>
       </c>
       <c r="AT14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O15" s="21">
         <v>0.35</v>
@@ -4056,22 +4056,22 @@
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O16" s="21">
         <v>0.42</v>
@@ -4159,25 +4159,25 @@
     </row>
     <row r="17" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O17" s="21">
         <v>0.81</v>
@@ -4274,25 +4274,25 @@
     </row>
     <row r="18" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O18" s="21">
         <v>0.86</v>
@@ -4389,25 +4389,25 @@
     </row>
     <row r="19" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O19" s="21">
         <v>0.9</v>
@@ -4502,30 +4502,30 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AT19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O20" s="21">
         <v>0.93</v>
@@ -4622,25 +4622,25 @@
     </row>
     <row r="21" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O21" s="21">
         <v>0.94</v>
@@ -4737,22 +4737,22 @@
     </row>
     <row r="22" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" t="s">
         <v>181</v>
       </c>
-      <c r="D22" t="s">
-        <v>182</v>
-      </c>
       <c r="J22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O22" s="21">
         <v>0.81</v>
@@ -4835,22 +4835,22 @@
     </row>
     <row r="23" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
+        <v>180</v>
+      </c>
+      <c r="D23" t="s">
         <v>181</v>
       </c>
-      <c r="D23" t="s">
-        <v>182</v>
-      </c>
       <c r="J23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O23" s="21">
         <v>0.88</v>
@@ -4933,22 +4933,22 @@
     </row>
     <row r="24" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
+        <v>180</v>
+      </c>
+      <c r="D24" t="s">
         <v>181</v>
       </c>
-      <c r="D24" t="s">
-        <v>182</v>
-      </c>
       <c r="J24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O24" s="21">
         <v>0.9</v>
@@ -5029,27 +5029,27 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AT24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
+        <v>180</v>
+      </c>
+      <c r="D25" t="s">
         <v>181</v>
       </c>
-      <c r="D25" t="s">
-        <v>182</v>
-      </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O25" s="21">
         <v>0.92</v>
@@ -5132,22 +5132,22 @@
     </row>
     <row r="26" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" t="s">
         <v>181</v>
       </c>
-      <c r="D26" t="s">
-        <v>182</v>
-      </c>
       <c r="J26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O26" s="21">
         <v>0.94</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="27" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O27" s="22">
         <v>0.23</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="28" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O28" s="22">
         <v>0.31</v>
@@ -5436,22 +5436,22 @@
     </row>
     <row r="29" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O29" s="22">
         <v>0.33</v>
@@ -5537,27 +5537,27 @@
         <v>0.9</v>
       </c>
       <c r="AT29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O30" s="22">
         <v>0.35</v>
@@ -5645,22 +5645,22 @@
     </row>
     <row r="31" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O31" s="22">
         <v>0.42</v>
@@ -5747,25 +5747,25 @@
     </row>
     <row r="32" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O32" s="22">
         <v>0.81</v>
@@ -5862,25 +5862,25 @@
     </row>
     <row r="33" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O33" s="22">
         <v>0.86</v>
@@ -5977,25 +5977,25 @@
     </row>
     <row r="34" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O34" s="22">
         <v>0.9</v>
@@ -6090,30 +6090,30 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AT34" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O35" s="22">
         <v>0.93</v>
@@ -6210,25 +6210,25 @@
     </row>
     <row r="36" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O36" s="22">
         <v>0.94</v>
@@ -6325,22 +6325,22 @@
     </row>
     <row r="37" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" t="s">
         <v>186</v>
       </c>
-      <c r="D37" t="s">
-        <v>187</v>
-      </c>
       <c r="J37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O37" s="22">
         <v>0.81</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="38" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" t="s">
         <v>186</v>
       </c>
-      <c r="D38" t="s">
-        <v>187</v>
-      </c>
       <c r="J38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O38" s="22">
         <v>0.88</v>
@@ -6521,22 +6521,22 @@
     </row>
     <row r="39" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39" t="s">
+        <v>185</v>
+      </c>
+      <c r="D39" t="s">
         <v>186</v>
       </c>
-      <c r="D39" t="s">
-        <v>187</v>
-      </c>
       <c r="J39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O39" s="22">
         <v>0.92</v>
@@ -6617,27 +6617,27 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AT39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
+        <v>185</v>
+      </c>
+      <c r="D40" t="s">
         <v>186</v>
       </c>
-      <c r="D40" t="s">
-        <v>187</v>
-      </c>
       <c r="J40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O40" s="22">
         <v>0.94</v>
@@ -6720,22 +6720,22 @@
     </row>
     <row r="41" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" t="s">
+        <v>185</v>
+      </c>
+      <c r="D41" t="s">
         <v>186</v>
       </c>
-      <c r="D41" t="s">
-        <v>187</v>
-      </c>
       <c r="J41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O41" s="22">
         <v>0.95</v>
